--- a/RiskHalo_Certification_Challenge/data/Weekly_Trade_Data_Uploads/Week_12_Trade_data.xlsx
+++ b/RiskHalo_Certification_Challenge/data/Weekly_Trade_Data_Uploads/Week_12_Trade_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SOFTWARES\CodeRepo\AIE9_CERTIFICATION_CHALLENGE\RiskHalo_Certification_Challenge\data\Weekly_Trade_Data_Uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD54373-E196-459C-8F00-4C0D5F25AC28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{812C2F7F-A91C-41F1-A3D3-74E92B7D90A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="33">
   <si>
     <t>Sr.</t>
   </si>
@@ -55,37 +55,58 @@
     <t>Turnover</t>
   </si>
   <si>
-    <t>OPT JIOFIN 31 Jul 2025 320 CE</t>
-  </si>
-  <si>
-    <t>30-06-2025</t>
-  </si>
-  <si>
-    <t>OPT GODREJPROP 31 Jul 2025 2400 PE</t>
-  </si>
-  <si>
-    <t>OPT NIFTY 03 Jul 2025 25600 PE</t>
-  </si>
-  <si>
-    <t>OPT NIFTY 03 Jul 2025 25500 CE</t>
-  </si>
-  <si>
-    <t>01-07-2025</t>
-  </si>
-  <si>
-    <t>OPT COFORGE 31 Jul 2025 1940 CE</t>
-  </si>
-  <si>
-    <t>OPT COFORGE 31 Jul 2025 1900 CE</t>
-  </si>
-  <si>
-    <t>OPT APLAPOLLO 31 Jul 2025 1760 PE</t>
-  </si>
-  <si>
-    <t>02-07-2025</t>
-  </si>
-  <si>
-    <t>OPT NBCC 31 Jul 2025 120 PE</t>
+    <t>OPT SUNPHARMA 28 Aug 2025 1620 PE</t>
+  </si>
+  <si>
+    <t>04-08-2025</t>
+  </si>
+  <si>
+    <t>OPT DLF 28 Aug 2025 760 PE</t>
+  </si>
+  <si>
+    <t>05-08-2025</t>
+  </si>
+  <si>
+    <t>OPT COLPAL 28 Aug 2025 2240 CE</t>
+  </si>
+  <si>
+    <t>OPT COALINDIA 28 Aug 2025 375 PE</t>
+  </si>
+  <si>
+    <t>OPT BSE 28 Aug 2025 2400 PE</t>
+  </si>
+  <si>
+    <t>OPT BOSCHLTD 28 Aug 2025 41000 CE</t>
+  </si>
+  <si>
+    <t>OPT AUROPHARMA 28 Aug 2025 1100 PE</t>
+  </si>
+  <si>
+    <t>OPT BEL 28 Aug 2025 400 CE</t>
+  </si>
+  <si>
+    <t>06-08-2025</t>
+  </si>
+  <si>
+    <t>OPT KAYNES 28 Aug 2025 6200 PE</t>
+  </si>
+  <si>
+    <t>OPT APLAPOLLO 28 Aug 2025 1560 PE</t>
+  </si>
+  <si>
+    <t>07-08-2025</t>
+  </si>
+  <si>
+    <t>OPT DIVISLAB 28 Aug 2025 6100 PE</t>
+  </si>
+  <si>
+    <t>OPT DIVISLAB 28 Aug 2025 6000 PE</t>
+  </si>
+  <si>
+    <t>OPT SYNGENE 28 Aug 2025 670 PE</t>
+  </si>
+  <si>
+    <t>OPT ZYDUSLIFE 28 Aug 2025 930 CE</t>
   </si>
   <si>
     <t>Buy Qty</t>
@@ -438,10 +459,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="32.7109375" customWidth="1"/>
+    <col min="2" max="2" width="34.28515625" customWidth="1"/>
     <col min="3" max="3" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.140625" style="1"/>
   </cols>
@@ -457,10 +478,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -469,10 +490,10 @@
         <v>4</v>
       </c>
       <c r="H1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="I1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J1" t="s">
         <v>5</v>
@@ -495,378 +516,660 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>143</v>
+        <v>254</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="1">
-        <v>45838</v>
+        <v>45873</v>
       </c>
       <c r="D2">
-        <v>2350</v>
+        <v>700</v>
       </c>
       <c r="E2">
-        <v>18.45</v>
+        <v>36.6</v>
       </c>
       <c r="F2">
-        <v>43357.5</v>
+        <v>25620</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H2">
-        <v>2350</v>
+        <v>700</v>
       </c>
       <c r="I2">
-        <v>17.55</v>
+        <v>33.799999999999997</v>
       </c>
       <c r="J2">
-        <v>41242.5</v>
+        <v>23660</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>-2115</v>
+        <v>-1960</v>
       </c>
       <c r="M2">
-        <v>124.66</v>
+        <v>92.92</v>
       </c>
       <c r="N2">
-        <v>-2239.66</v>
+        <v>-2052.92</v>
       </c>
       <c r="O2">
-        <v>2115</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
       </c>
       <c r="C3" s="1">
-        <v>45838</v>
+        <v>45874</v>
       </c>
       <c r="D3">
-        <v>275</v>
+        <v>825</v>
       </c>
       <c r="E3">
-        <v>116.4</v>
+        <v>16.350000000000001</v>
       </c>
       <c r="F3">
-        <v>32010</v>
+        <v>13488.75</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H3">
-        <v>275</v>
+        <v>825</v>
       </c>
       <c r="I3">
-        <v>112</v>
+        <v>14.55</v>
       </c>
       <c r="J3">
-        <v>30800</v>
+        <v>12003.75</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>-1210</v>
+        <v>-1485</v>
       </c>
       <c r="M3">
-        <v>105.37</v>
+        <v>70.319999999999993</v>
       </c>
       <c r="N3">
-        <v>-1315.37</v>
+        <v>-1555.32</v>
       </c>
       <c r="O3">
-        <v>1210</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>216</v>
+        <v>67</v>
       </c>
       <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="1">
+        <v>45874</v>
+      </c>
+      <c r="D4">
+        <v>225</v>
+      </c>
+      <c r="E4">
+        <v>53.6</v>
+      </c>
+      <c r="F4">
+        <v>12060</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="1">
-        <v>45838</v>
-      </c>
-      <c r="D4">
-        <v>300</v>
-      </c>
-      <c r="E4">
-        <v>129</v>
-      </c>
-      <c r="F4">
-        <v>38700</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H4">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="I4">
-        <v>133.97999999999999</v>
+        <v>52.3</v>
       </c>
       <c r="J4">
-        <v>40192.5</v>
+        <v>11767.5</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>1492.5</v>
+        <v>-292.5</v>
       </c>
       <c r="M4">
-        <v>216.12</v>
+        <v>69.349999999999994</v>
       </c>
       <c r="N4">
-        <v>1276.3800000000001</v>
+        <v>-361.85</v>
       </c>
       <c r="O4">
-        <v>1492.5</v>
+        <v>292.5</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>214</v>
+        <v>58</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1">
-        <v>45839</v>
+        <v>45874</v>
       </c>
       <c r="D5">
-        <v>300</v>
+        <v>1350</v>
       </c>
       <c r="E5">
-        <v>127.85</v>
+        <v>12.5</v>
       </c>
       <c r="F5">
-        <v>38355</v>
+        <v>16875</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H5">
-        <v>300</v>
+        <v>1350</v>
       </c>
       <c r="I5">
-        <v>121.08</v>
+        <v>12.15</v>
       </c>
       <c r="J5">
-        <v>36322.5</v>
+        <v>16402.5</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>-2032.5</v>
+        <v>-472.5</v>
       </c>
       <c r="M5">
-        <v>163.27000000000001</v>
+        <v>78.099999999999994</v>
       </c>
       <c r="N5">
-        <v>-2195.77</v>
+        <v>-550.6</v>
       </c>
       <c r="O5">
-        <v>2032.5</v>
+        <v>472.5</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="B6" t="s">
         <v>17</v>
       </c>
       <c r="C6" s="1">
-        <v>45839</v>
+        <v>45874</v>
       </c>
       <c r="D6">
-        <v>375</v>
+        <v>1125</v>
       </c>
       <c r="E6">
-        <v>88.8</v>
+        <v>119.03</v>
       </c>
       <c r="F6">
-        <v>33300</v>
+        <v>133912.5</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H6">
-        <v>375</v>
+        <v>1125</v>
       </c>
       <c r="I6">
-        <v>88.85</v>
+        <v>109.32</v>
       </c>
       <c r="J6">
-        <v>33318.75</v>
+        <v>122981.25</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>18.75</v>
+        <v>-10931.25</v>
       </c>
       <c r="M6">
-        <v>109.53</v>
+        <v>352.98</v>
       </c>
       <c r="N6">
-        <v>-90.78</v>
+        <v>-11284.23</v>
       </c>
       <c r="O6">
-        <v>18.75</v>
+        <v>10931.25</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B7" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="1">
-        <v>45839</v>
+        <v>45874</v>
       </c>
       <c r="D7">
-        <v>375</v>
+        <v>25</v>
       </c>
       <c r="E7">
-        <v>103.3</v>
+        <v>1195.0999999999999</v>
       </c>
       <c r="F7">
-        <v>38737.5</v>
+        <v>29877.5</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H7">
-        <v>375</v>
+        <v>25</v>
       </c>
       <c r="I7">
-        <v>97.25</v>
+        <v>1170.05</v>
       </c>
       <c r="J7">
-        <v>36468.75</v>
+        <v>29251.25</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>-2268.75</v>
+        <v>-626.25</v>
       </c>
       <c r="M7">
-        <v>116.03</v>
+        <v>102.21</v>
       </c>
       <c r="N7">
-        <v>-2384.7800000000002</v>
+        <v>-728.46</v>
       </c>
       <c r="O7">
-        <v>2268.75</v>
+        <v>626.25</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
         <v>19</v>
       </c>
       <c r="C8" s="1">
-        <v>45840</v>
+        <v>45874</v>
       </c>
       <c r="D8">
-        <v>350</v>
+        <v>1100</v>
       </c>
       <c r="E8">
-        <v>53.55</v>
+        <v>45.85</v>
       </c>
       <c r="F8">
-        <v>18742.5</v>
+        <v>50435</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H8">
-        <v>350</v>
+        <v>1100</v>
       </c>
       <c r="I8">
-        <v>59.1</v>
+        <v>47.2</v>
       </c>
       <c r="J8">
-        <v>20685</v>
+        <v>51920</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>1942.5</v>
+        <v>1485</v>
       </c>
       <c r="M8">
-        <v>85.03</v>
+        <v>190.86</v>
       </c>
       <c r="N8">
-        <v>1857.47</v>
+        <v>1294.1400000000001</v>
       </c>
       <c r="O8">
-        <v>1942.5</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>182</v>
+        <v>42</v>
       </c>
       <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="1">
+        <v>45875</v>
+      </c>
+      <c r="D9">
+        <v>2850</v>
+      </c>
+      <c r="E9">
+        <v>6.55</v>
+      </c>
+      <c r="F9">
+        <v>18667.5</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="1">
-        <v>45840</v>
-      </c>
-      <c r="D9">
-        <v>13000</v>
-      </c>
-      <c r="E9">
-        <v>5.03</v>
-      </c>
-      <c r="F9">
-        <v>65325</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="H9">
-        <v>13000</v>
+        <v>2850</v>
       </c>
       <c r="I9">
-        <v>4.83</v>
+        <v>5.5</v>
       </c>
       <c r="J9">
-        <v>62725</v>
+        <v>15675</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>-2600</v>
+        <v>-2992.5</v>
       </c>
       <c r="M9">
-        <v>213</v>
+        <v>77.88</v>
       </c>
       <c r="N9">
-        <v>-2813</v>
+        <v>-3070.38</v>
       </c>
       <c r="O9">
-        <v>2600</v>
+        <v>2992.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>154</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1">
+        <v>45875</v>
+      </c>
+      <c r="D10">
+        <v>200</v>
+      </c>
+      <c r="E10">
+        <v>246.35</v>
+      </c>
+      <c r="F10">
+        <v>49270</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10">
+        <v>200</v>
+      </c>
+      <c r="I10">
+        <v>262.8</v>
+      </c>
+      <c r="J10">
+        <v>52560</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>3290</v>
+      </c>
+      <c r="M10">
+        <v>190.97</v>
+      </c>
+      <c r="N10">
+        <v>3099.03</v>
+      </c>
+      <c r="O10">
+        <v>3290</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1">
+        <v>45876</v>
+      </c>
+      <c r="D11">
+        <v>350</v>
+      </c>
+      <c r="E11">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="F11">
+        <v>13195</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11">
+        <v>350</v>
+      </c>
+      <c r="I11">
+        <v>34.75</v>
+      </c>
+      <c r="J11">
+        <v>12162.5</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>-1032.5</v>
+      </c>
+      <c r="M11">
+        <v>70.42</v>
+      </c>
+      <c r="N11">
+        <v>-1102.92</v>
+      </c>
+      <c r="O11">
+        <v>1032.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>84</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="1">
+        <v>45876</v>
+      </c>
+      <c r="D12">
+        <v>100</v>
+      </c>
+      <c r="E12">
+        <v>149.9</v>
+      </c>
+      <c r="F12">
+        <v>14990</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12">
+        <v>100</v>
+      </c>
+      <c r="I12">
+        <v>197</v>
+      </c>
+      <c r="J12">
+        <v>19700</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>4710</v>
+      </c>
+      <c r="M12">
+        <v>81.93</v>
+      </c>
+      <c r="N12">
+        <v>4628.07</v>
+      </c>
+      <c r="O12">
+        <v>4710</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>82</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="1">
+        <v>45876</v>
+      </c>
+      <c r="D13">
+        <v>400</v>
+      </c>
+      <c r="E13">
+        <v>125.09</v>
+      </c>
+      <c r="F13">
+        <v>50035</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13">
+        <v>400</v>
+      </c>
+      <c r="I13">
+        <v>105.95</v>
+      </c>
+      <c r="J13">
+        <v>42380</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>-7655</v>
+      </c>
+      <c r="M13">
+        <v>200.86</v>
+      </c>
+      <c r="N13">
+        <v>-7855.86</v>
+      </c>
+      <c r="O13">
+        <v>7655</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>256</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="1">
+        <v>45876</v>
+      </c>
+      <c r="D14">
+        <v>1000</v>
+      </c>
+      <c r="E14">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="F14">
+        <v>18100</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H14">
+        <v>1000</v>
+      </c>
+      <c r="I14">
+        <v>18.3</v>
+      </c>
+      <c r="J14">
+        <v>18300</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>200</v>
+      </c>
+      <c r="M14">
+        <v>81.34</v>
+      </c>
+      <c r="N14">
+        <v>118.66</v>
+      </c>
+      <c r="O14">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>289</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="1">
+        <v>45876</v>
+      </c>
+      <c r="D15">
+        <v>900</v>
+      </c>
+      <c r="E15">
+        <v>33.5</v>
+      </c>
+      <c r="F15">
+        <v>30150</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H15">
+        <v>900</v>
+      </c>
+      <c r="I15">
+        <v>29.5</v>
+      </c>
+      <c r="J15">
+        <v>26550</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>-3600</v>
+      </c>
+      <c r="M15">
+        <v>98.49</v>
+      </c>
+      <c r="N15">
+        <v>-3698.49</v>
+      </c>
+      <c r="O15">
+        <v>3600</v>
       </c>
     </row>
   </sheetData>
